--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46209.62458533565</v>
+        <v>46279.167964039356</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -520,325 +520,325 @@
     <t>Fabricación estructura proveedor externo,Generacion OC Fabricación Externa</t>
   </si>
   <si>
+    <t>1214995680413416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación estructura proveedor externo,Fabricación Externa </t>
+  </si>
+  <si>
+    <t>1214982388058454</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa ,Control de calidad fabricación externa ,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214982388058471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad fabricación externa </t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214982595261918</t>
+  </si>
+  <si>
+    <t>Mecanizado</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado,Fabricación Mecanizado</t>
+  </si>
+  <si>
+    <t>1214982595261930</t>
+  </si>
+  <si>
+    <t>Mecanizado,Fabricación Mecanizado</t>
+  </si>
+  <si>
+    <t>1214995680427506</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado</t>
+  </si>
+  <si>
+    <t>1214969047721209</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214995680427525</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214995680435931</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214995680437154</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,propuesta Corte Laser,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,Propuesta Corte plasma ,Propuesta Mecanizado,Propuesta Fabricación externa ,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>1214982817921526</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>1214982817921538</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214982817946368</t>
+  </si>
+  <si>
+    <t>1214982817946380</t>
+  </si>
+  <si>
+    <t>1214982817946387</t>
+  </si>
+  <si>
+    <t>1214982817921593</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214982817921605</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214982388114004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>1214982595357394</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214982595357416</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>1214982595357913</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214982595357930</t>
+  </si>
+  <si>
+    <t>1214982818018118</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Armado,Preparación Materiales,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214982818018130</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>1214982595382876</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1214982595392257</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214982818021826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>1214982818021853</t>
+  </si>
+  <si>
+    <t>1214982580553482</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1214982580553563</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,check planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>1214982508670057</t>
+  </si>
+  <si>
+    <t>1214982508670079</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,Armado</t>
+  </si>
+  <si>
+    <t>1214982818063794</t>
+  </si>
+  <si>
+    <t>1214982818094143</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214982818122342</t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4326- ZVN 1-12-55/4,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214982818122364</t>
+  </si>
+  <si>
+    <t>Revestimiento,Control de calidad Armado,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>1214982595527091</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>1214982388250864</t>
+  </si>
+  <si>
+    <t>1214982595569991</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214982595570003</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,Bodega:,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>1214982580659568</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,Bodega:,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214995680413416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación estructura proveedor externo,Fabricación Externa </t>
-  </si>
-  <si>
-    <t>1214982388058454</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa ,Control de calidad fabricación externa ,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214982388058471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad fabricación externa </t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214982595261918</t>
-  </si>
-  <si>
-    <t>Mecanizado</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado,Fabricación Mecanizado</t>
-  </si>
-  <si>
-    <t>1214982595261930</t>
-  </si>
-  <si>
-    <t>Mecanizado,Fabricación Mecanizado</t>
-  </si>
-  <si>
-    <t>1214995680427506</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado</t>
-  </si>
-  <si>
-    <t>1214969047721209</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214995680427525</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214995680435931</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214995680437154</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,propuesta Corte Laser,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,Propuesta Corte plasma ,Propuesta Mecanizado,Propuesta Fabricación externa ,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>1214982817921526</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>1214982817921538</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214982817946368</t>
-  </si>
-  <si>
-    <t>1214982817946380</t>
-  </si>
-  <si>
-    <t>1214982817946387</t>
-  </si>
-  <si>
-    <t>1214982817921593</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214982817921605</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214982388114004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>1214982595357394</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214982595357416</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>1214982595357913</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214982595357930</t>
-  </si>
-  <si>
-    <t>1214982818018118</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Armado,Preparación Materiales,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214982818018130</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>1214982595382876</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1214982595392257</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214982818021826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>1214982818021853</t>
-  </si>
-  <si>
-    <t>1214982580553482</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1214982580553563</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,check planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>1214982508670057</t>
-  </si>
-  <si>
-    <t>1214982508670079</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,Armado</t>
-  </si>
-  <si>
-    <t>1214982818063794</t>
-  </si>
-  <si>
-    <t>1214982818094143</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214982818122342</t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4326- ZVN 1-12-55/4,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214982818122364</t>
-  </si>
-  <si>
-    <t>Revestimiento,Control de calidad Armado,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>1214982595527091</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>1214982388250864</t>
-  </si>
-  <si>
-    <t>1214982595569991</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214982595570003</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,Bodega:,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>1214982580659568</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,Bodega:,OT 4326- ZVN 1-12-55/4</t>
   </si>
   <si>
     <t>1214982388272056</t>
@@ -3910,7 +3910,7 @@
         <v>46209.624663807874</v>
       </c>
       <c r="D38" s="5">
-        <v>46272.13554642361</v>
+        <v>46280.13930923611</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3954,8 +3954,8 @@
       <c r="R38" s="5">
         <v>46279</v>
       </c>
-      <c r="S38" s="12" t="s">
-        <v>149</v>
+      <c r="S38" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46162.792089166665</v>
@@ -4011,7 +4011,7 @@
         <v>87</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4021,7 +4021,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46162.792093599535</v>
@@ -4033,7 +4033,7 @@
         <v>46209.62457706018</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4066,7 +4066,7 @@
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4076,7 +4076,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46162.79210385417</v>
@@ -4086,16 +4086,16 @@
         <v>46279.167964039356</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
+      <c r="H41" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I41" s="9">
         <v>46279</v>
@@ -4116,7 +4116,7 @@
         <v>145</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46162.79210730324</v>
@@ -4141,7 +4141,7 @@
         <v>46252.17961203704</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4171,7 +4171,7 @@
         <v>90</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46162.792111180555</v>
@@ -4233,13 +4233,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>84</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4249,7 +4249,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46162.79211601852</v>
@@ -4261,7 +4261,7 @@
         <v>46205.61212924769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4288,13 +4288,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46162.791800798615</v>
@@ -4316,7 +4316,7 @@
         <v>46210.52939782407</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>25</v>
@@ -4340,7 +4340,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
@@ -4357,7 +4357,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46162.79212121527</v>
@@ -4369,16 +4369,16 @@
         <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I46" s="5">
         <v>46160</v>
@@ -4396,13 +4396,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>58</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="5">
         <v>46160</v>
@@ -4422,7 +4422,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46162.79212670139</v>
@@ -4434,16 +4434,16 @@
         <v>46234.17771361111</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="I47" s="9">
         <v>46216</v>
@@ -4461,13 +4461,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="Q47" s="9">
         <v>46216</v>
@@ -4487,7 +4487,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46162.792133090275</v>
@@ -4505,10 +4505,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I48" s="5">
         <v>46234</v>
@@ -4526,13 +4526,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46234</v>
@@ -4552,7 +4552,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46162.79214709491</v>
@@ -4564,16 +4564,16 @@
         <v>46258.5437854051</v>
       </c>
       <c r="E49" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I49" s="9">
         <v>46322</v>
@@ -4591,10 +4591,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4617,7 +4617,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46162.792150775465</v>
@@ -4627,16 +4627,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4654,13 +4654,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4670,7 +4670,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792154849536</v>
@@ -4680,16 +4680,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4707,13 +4707,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4723,7 +4723,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46162.79215875</v>
@@ -4733,16 +4733,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4760,13 +4760,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79216164352</v>
@@ -4786,16 +4786,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4813,13 +4813,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4829,7 +4829,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46162.7922118287</v>
@@ -4841,7 +4841,7 @@
         <v>46217.58833277778</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4865,7 +4865,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922200926</v>
@@ -4894,16 +4894,16 @@
         <v>46254.173978101855</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
+      <c r="H55" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I55" s="9">
         <v>46252</v>
@@ -4921,13 +4921,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>134</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q55" s="9">
         <v>46252</v>
@@ -4947,7 +4947,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46162.792225625</v>
@@ -4959,16 +4959,16 @@
         <v>46256.17331716436</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4986,13 +4986,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -5012,7 +5012,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
         <v>46162.79223230324</v>
@@ -5024,16 +5024,16 @@
         <v>46254.17397791667</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I57" s="9">
         <v>46252</v>
@@ -5051,13 +5051,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>142</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q57" s="9">
         <v>46252</v>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223737269</v>
@@ -5089,16 +5089,16 @@
         <v>46256.17331711805</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -5116,13 +5116,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5142,7 +5142,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B59" s="9">
         <v>46162.7922424537</v>
@@ -5154,16 +5154,16 @@
         <v>46254.173977997685</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I59" s="9">
         <v>46252</v>
@@ -5181,13 +5181,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="9">
         <v>46252</v>
@@ -5207,7 +5207,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46162.792246909725</v>
@@ -5219,16 +5219,16 @@
         <v>46256.173317152774</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5246,13 +5246,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5272,7 +5272,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B61" s="9">
         <v>46162.79225168981</v>
@@ -5284,7 +5284,7 @@
         <v>46249.391917719906</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5308,7 +5308,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5325,7 +5325,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46162.792254479165</v>
@@ -5337,16 +5337,16 @@
         <v>46267.20458883102</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5364,13 +5364,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -5390,7 +5390,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5402,16 +5402,16 @@
         <v>46245.69551650463</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5429,13 +5429,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5445,7 +5445,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5457,16 +5457,16 @@
         <v>46245.695510509264</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5484,13 +5484,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5500,7 +5500,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5512,16 +5512,16 @@
         <v>46245.695528564815</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5539,13 +5539,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5555,7 +5555,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5567,16 +5567,16 @@
         <v>46245.69553246528</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5594,13 +5594,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5622,16 +5622,16 @@
         <v>46249.076454594906</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I67" s="9">
         <v>46267</v>
@@ -5649,13 +5649,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="9">
         <v>46267</v>
@@ -5675,7 +5675,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5687,16 +5687,16 @@
         <v>46245.69562136574</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5714,13 +5714,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5730,7 +5730,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5742,16 +5742,16 @@
         <v>46245.69562572917</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5769,13 +5769,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5785,7 +5785,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5797,16 +5797,16 @@
         <v>46245.69563821759</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5824,13 +5824,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5840,7 +5840,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5852,16 +5852,16 @@
         <v>46245.69564313657</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5879,13 +5879,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5895,7 +5895,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5907,16 +5907,16 @@
         <v>46249.07653208333</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I72" s="5">
         <v>46289</v>
@@ -5934,13 +5934,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q72" s="5">
         <v>46289</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5972,16 +5972,16 @@
         <v>46245.69567159722</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I73" s="9">
         <v>46289</v>
@@ -5999,13 +5999,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -6027,16 +6027,16 @@
         <v>46245.695676979165</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -6054,13 +6054,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6070,7 +6070,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6082,16 +6082,16 @@
         <v>46245.69568078704</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I75" s="9">
         <v>46289</v>
@@ -6109,13 +6109,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6137,16 +6137,16 @@
         <v>46245.69568829861</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -6164,13 +6164,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6180,7 +6180,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6190,7 +6190,7 @@
         <v>46212.65565390047</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6214,7 +6214,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6229,7 +6229,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6241,16 +6241,16 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I78" s="5">
         <v>46169</v>
@@ -6268,13 +6268,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6294,7 +6294,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6306,16 +6306,16 @@
         <v>46273.1659766088</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I79" s="9">
         <v>46279</v>
@@ -6333,13 +6333,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>102</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6348,7 +6348,7 @@
         <v>46280</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6377,10 +6377,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I80" s="5">
         <v>46302</v>
@@ -6398,13 +6398,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>120</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q80" s="5">
         <v>46302</v>
@@ -6440,10 +6440,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I81" s="9">
         <v>46280</v>
@@ -6461,10 +6461,10 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>260</v>
@@ -6476,7 +6476,7 @@
         <v>46281</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
@@ -6615,7 +6615,7 @@
         <v>46245.695676504634</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6668,7 +6668,7 @@
         <v>46245.69568125</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6721,7 +6721,7 @@
         <v>46245.695686527775</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6751,7 +6751,7 @@
         <v>265</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>271</v>
@@ -6774,7 +6774,7 @@
         <v>46245.69569986111</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6804,7 +6804,7 @@
         <v>265</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>273</v>
@@ -6859,7 +6859,7 @@
         <v>262</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>262</v>
@@ -6892,7 +6892,7 @@
         <v>46223.576037604165</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6945,7 +6945,7 @@
         <v>46223.57603699074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6998,7 +6998,7 @@
         <v>46223.57603633102</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7051,7 +7051,7 @@
         <v>46223.576035659724</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7136,7 +7136,7 @@
         <v>262</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>262</v>
@@ -7169,7 +7169,7 @@
         <v>46223.5761230787</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7222,7 +7222,7 @@
         <v>46223.57612246528</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7275,7 +7275,7 @@
         <v>46223.57612182871</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7328,7 +7328,7 @@
         <v>46223.57612121528</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7413,7 +7413,7 @@
         <v>262</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>262</v>
@@ -7446,7 +7446,7 @@
         <v>46223.57621322917</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7499,7 +7499,7 @@
         <v>46223.576212500004</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7552,7 +7552,7 @@
         <v>46223.57621184028</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7605,7 +7605,7 @@
         <v>46223.57621119213</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7690,7 +7690,7 @@
         <v>262</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>262</v>
@@ -7723,7 +7723,7 @@
         <v>46223.57630975694</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7753,7 +7753,7 @@
         <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>307</v>
@@ -7776,7 +7776,7 @@
         <v>46223.57630916667</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7806,7 +7806,7 @@
         <v>305</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>309</v>
@@ -7829,7 +7829,7 @@
         <v>46223.57630858796</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7859,7 +7859,7 @@
         <v>305</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>309</v>
@@ -7882,7 +7882,7 @@
         <v>46223.57630797454</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7912,7 +7912,7 @@
         <v>305</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>309</v>
@@ -7965,7 +7965,7 @@
         <v>262</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>314</v>
@@ -7998,7 +7998,7 @@
         <v>46223.5763915162</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8028,7 +8028,7 @@
         <v>313</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>316</v>
@@ -8051,7 +8051,7 @@
         <v>46223.576390856484</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8081,7 +8081,7 @@
         <v>313</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>316</v>
@@ -8104,7 +8104,7 @@
         <v>46223.57639018519</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8134,7 +8134,7 @@
         <v>313</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>316</v>
@@ -8157,7 +8157,7 @@
         <v>46223.57638950231</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8187,7 +8187,7 @@
         <v>313</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>316</v>
@@ -8320,7 +8320,7 @@
         <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8350,7 +8350,7 @@
         <v>324</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>329</v>
@@ -8373,7 +8373,7 @@
         <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8403,7 +8403,7 @@
         <v>324</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>329</v>
@@ -8426,7 +8426,7 @@
         <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8456,7 +8456,7 @@
         <v>324</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>332</v>
@@ -8479,7 +8479,7 @@
         <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8509,7 +8509,7 @@
         <v>324</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>332</v>
@@ -8564,7 +8564,7 @@
         <v>321</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>321</v>
@@ -8597,7 +8597,7 @@
         <v>46223.57651084491</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8627,7 +8627,7 @@
         <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>337</v>
@@ -8650,7 +8650,7 @@
         <v>46223.57651017361</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8680,7 +8680,7 @@
         <v>335</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>337</v>
@@ -8703,7 +8703,7 @@
         <v>46223.57650946759</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8733,7 +8733,7 @@
         <v>335</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>340</v>
@@ -8756,7 +8756,7 @@
         <v>46223.57650879629</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8786,7 +8786,7 @@
         <v>335</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>337</v>
@@ -8817,10 +8817,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I124" s="5">
         <v>46328</v>
@@ -8841,7 +8841,7 @@
         <v>321</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>321</v>
@@ -8876,16 +8876,16 @@
         <v>46260.596735405095</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8906,7 +8906,7 @@
         <v>343</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>345</v>
@@ -8929,16 +8929,16 @@
         <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8959,7 +8959,7 @@
         <v>343</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>345</v>
@@ -8982,16 +8982,16 @@
         <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -9012,7 +9012,7 @@
         <v>343</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>348</v>
@@ -9035,16 +9035,16 @@
         <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -9065,7 +9065,7 @@
         <v>343</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>350</v>
@@ -9096,10 +9096,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I129" s="9">
         <v>46329</v>
@@ -9120,7 +9120,7 @@
         <v>321</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>353</v>
@@ -9153,16 +9153,16 @@
         <v>46260.59674087963</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -9183,7 +9183,7 @@
         <v>352</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>352</v>
@@ -9206,16 +9206,16 @@
         <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9236,7 +9236,7 @@
         <v>352</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>352</v>
@@ -9259,16 +9259,16 @@
         <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9289,7 +9289,7 @@
         <v>352</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>352</v>
@@ -9312,16 +9312,16 @@
         <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9342,7 +9342,7 @@
         <v>352</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P133" s="10" t="s">
         <v>352</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -766,6 +766,9 @@
     <t>Armado</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214982580553563</t>
   </si>
   <si>
@@ -836,9 +839,6 @@
   </si>
   <si>
     <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,Bodega:,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214982388272056</t>
@@ -5619,7 +5619,7 @@
         <v>46245.69565657407</v>
       </c>
       <c r="D67" s="9">
-        <v>46249.076454594906</v>
+        <v>46281.13097175926</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5663,8 +5663,8 @@
       <c r="R67" s="9">
         <v>46288</v>
       </c>
-      <c r="S67" s="7" t="s">
-        <v>52</v>
+      <c r="S67" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="T67" s="10">
         <v>1</v>
@@ -5675,7 +5675,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5717,10 +5717,10 @@
         <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5730,7 +5730,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5772,10 +5772,10 @@
         <v>230</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5785,7 +5785,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5827,10 +5827,10 @@
         <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5840,7 +5840,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5882,10 +5882,10 @@
         <v>230</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5895,7 +5895,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5907,7 +5907,7 @@
         <v>46249.07653208333</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5999,13 +5999,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -6054,13 +6054,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6070,7 +6070,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6109,13 +6109,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6164,13 +6164,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6180,7 +6180,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6214,7 +6214,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6229,7 +6229,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6241,7 +6241,7 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6274,7 +6274,7 @@
         <v>111</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6294,7 +6294,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6303,10 +6303,10 @@
         <v>46212.65527831019</v>
       </c>
       <c r="D79" s="9">
-        <v>46273.1659766088</v>
+        <v>46281.126626377314</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6339,7 +6339,7 @@
         <v>102</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6347,8 +6347,8 @@
       <c r="R79" s="9">
         <v>46280</v>
       </c>
-      <c r="S79" s="12" t="s">
-        <v>255</v>
+      <c r="S79" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46274.12921561343</v>
+        <v>46281.16775166667</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>259</v>
@@ -6476,7 +6476,7 @@
         <v>46281</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -6431,7 +6431,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46281.16775166667</v>
+        <v>46282.137175972224</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>259</v>
@@ -6475,8 +6475,8 @@
       <c r="R81" s="9">
         <v>46281</v>
       </c>
-      <c r="S81" s="12" t="s">
-        <v>231</v>
+      <c r="S81" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -5904,7 +5904,7 @@
         <v>46226.72415461806</v>
       </c>
       <c r="D72" s="5">
-        <v>46249.07653208333</v>
+        <v>46283.155639178236</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>240</v>
@@ -5948,8 +5948,8 @@
       <c r="R72" s="5">
         <v>46290</v>
       </c>
-      <c r="S72" s="7" t="s">
-        <v>52</v>
+      <c r="S72" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
